--- a/artfynd/A 41082-2024 artfynd.xlsx
+++ b/artfynd/A 41082-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>104467581</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41082-2024 artfynd.xlsx
+++ b/artfynd/A 41082-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>104467581</v>
       </c>
       <c r="B2" t="n">
-        <v>57960</v>
+        <v>57970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41082-2024 artfynd.xlsx
+++ b/artfynd/A 41082-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>104467581</v>
       </c>
       <c r="B2" t="n">
-        <v>57970</v>
+        <v>57971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41082-2024 artfynd.xlsx
+++ b/artfynd/A 41082-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>104467581</v>
       </c>
       <c r="B2" t="n">
-        <v>57971</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41082-2024 artfynd.xlsx
+++ b/artfynd/A 41082-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>104467581</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
